--- a/testing/12001800.xlsx
+++ b/testing/12001800.xlsx
@@ -439,13 +439,13 @@
         <v>Steel Grey/ True Black</v>
       </c>
       <c r="D2" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E2" t="str">
         <v>White</v>
       </c>
       <c r="F2" t="str">
-        <v>Back Yoke Full Back</v>
+        <v>Back Yoke, Full Back</v>
       </c>
       <c r="G2" t="str">
         <v>J354FSteelGreyTrueBlack-9953285_11845694-9.jpg</v>
@@ -468,7 +468,7 @@
         <v>True Navy/ True Navy</v>
       </c>
       <c r="D3" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E3" t="str">
         <v>White</v>
@@ -497,13 +497,13 @@
         <v>Black</v>
       </c>
       <c r="D4" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E4" t="str">
         <v>White</v>
       </c>
       <c r="F4" t="str">
-        <v>Full Front Right Chest Left Chest</v>
+        <v>Full Front, Right Chest ,Left Chest</v>
       </c>
       <c r="G4" t="str">
         <v>CSV60FBlack-9953285_11845694-1.jpg</v>
@@ -526,13 +526,13 @@
         <v>Deep Black</v>
       </c>
       <c r="D5" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E5" t="str">
         <v>White</v>
       </c>
       <c r="F5" t="str">
-        <v>Right Sleeve Left Chest</v>
+        <v>Right Sleeve, Left Chest</v>
       </c>
       <c r="G5" t="str">
         <v>L903FDeepBlack-10036294_11952741-46.jpg</v>
@@ -555,13 +555,13 @@
         <v>Deep Black</v>
       </c>
       <c r="D6" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E6" t="str">
         <v>White</v>
       </c>
       <c r="F6" t="str">
-        <v>Back Yoke Full Back</v>
+        <v>Back Yoke, Full Back</v>
       </c>
       <c r="G6" t="str">
         <v>F904FDeepBlack-10036294_11952742-9.jpg</v>
@@ -584,13 +584,13 @@
         <v>River Blue Navy</v>
       </c>
       <c r="D7" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E7" t="str">
         <v>White</v>
       </c>
       <c r="F7" t="str">
-        <v>Right Cuff Left Chest</v>
+        <v>Right Cuff ,Left Chest</v>
       </c>
       <c r="G7" t="str">
         <v>F239FRiverBlueNavy-10036294_11952742-16.jpg</v>
@@ -613,13 +613,13 @@
         <v>Shadow Grey</v>
       </c>
       <c r="D8" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E8" t="str">
         <v>White</v>
       </c>
       <c r="F8" t="str">
-        <v>Right Chest Left Hip</v>
+        <v>Right Chest, Left Hip</v>
       </c>
       <c r="G8" t="str">
         <v>CT104315FShadowGrey-10036294_11952739-24.jpg</v>
@@ -642,13 +642,13 @@
         <v>Deep Black</v>
       </c>
       <c r="D9" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E9" t="str">
         <v>White</v>
       </c>
       <c r="F9" t="str">
-        <v>Right Chest Left Hip</v>
+        <v>Right Chest, Left Hip</v>
       </c>
       <c r="G9" t="str">
         <v>L851FDeepBlack-10036294_11952742-24.jpg</v>
@@ -671,7 +671,7 @@
         <v>Dark Slate/ Black</v>
       </c>
       <c r="D10" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E10" t="str">
         <v>White</v>
@@ -700,13 +700,13 @@
         <v>True Navy</v>
       </c>
       <c r="D11" t="str">
-        <v>9953285_11845694</v>
+        <v>9953285_11845694,7849526_7811374</v>
       </c>
       <c r="E11" t="str">
         <v>White</v>
       </c>
       <c r="F11" t="str">
-        <v>Left Bicep Right Chest</v>
+        <v>Left Bicep ,Right Chest</v>
       </c>
       <c r="G11" t="str">
         <v>ST941FTrueNavy-10036294_11952741-20.jpg</v>
